--- a/Datas/NPCFunctionData.xlsx
+++ b/Datas/NPCFunctionData.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="NPCFunctionData" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -435,7 +435,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>

--- a/Datas/NPCFunctionData.xlsx
+++ b/Datas/NPCFunctionData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
   <si>
     <t>id</t>
   </si>
@@ -74,12 +74,25 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Bag</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Box</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>F_Get</t>
+  </si>
+  <si>
+    <t>F_Give</t>
+  </si>
+  <si>
+    <t>F_Hurt</t>
+  </si>
+  <si>
+    <t>F_Like</t>
+  </si>
+  <si>
+    <t>F_Love</t>
+  </si>
+  <si>
+    <t>F_Please</t>
+  </si>
+  <si>
+    <t>F_Shop</t>
   </si>
 </sst>
 </file>
@@ -102,12 +115,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -122,9 +141,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -456,11 +478,11 @@
       <c r="A4" s="1">
         <v>1</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -473,11 +495,11 @@
       <c r="A5" s="1">
         <v>2</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -490,11 +512,11 @@
       <c r="A6" s="1">
         <v>3</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
@@ -507,11 +529,11 @@
       <c r="A7" s="1">
         <v>4</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -524,11 +546,11 @@
       <c r="A8" s="1">
         <v>5</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -545,7 +567,7 @@
         <v>12</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -558,11 +580,11 @@
       <c r="A10" s="1">
         <v>7</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
@@ -575,11 +597,11 @@
       <c r="A11" s="1">
         <v>8</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>

--- a/Datas/NPCFunctionData.xlsx
+++ b/Datas/NPCFunctionData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
   <si>
     <t>id</t>
   </si>
@@ -74,25 +74,41 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>F_Give</t>
+  </si>
+  <si>
+    <t>F_Hurt</t>
+  </si>
+  <si>
+    <t>F_Like</t>
+  </si>
+  <si>
+    <t>F_Love</t>
+  </si>
+  <si>
+    <t>F_Please</t>
+  </si>
+  <si>
+    <t>F_Shop</t>
+  </si>
+  <si>
+    <t>分配</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>F_Get</t>
-  </si>
-  <si>
-    <t>F_Give</t>
-  </si>
-  <si>
-    <t>F_Hurt</t>
-  </si>
-  <si>
-    <t>F_Like</t>
-  </si>
-  <si>
-    <t>F_Love</t>
-  </si>
-  <si>
-    <t>F_Please</t>
-  </si>
-  <si>
-    <t>F_Shop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F_SetAnimal</t>
+  </si>
+  <si>
+    <t>放生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F_AnimalLeave</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -429,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:E11"/>
+  <dimension ref="A2:E13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -482,7 +498,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -499,7 +515,7 @@
         <v>8</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -516,7 +532,7 @@
         <v>9</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
@@ -533,7 +549,7 @@
         <v>10</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -550,7 +566,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -567,7 +583,7 @@
         <v>12</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -584,7 +600,7 @@
         <v>13</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
@@ -601,13 +617,47 @@
         <v>14</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
       </c>
       <c r="E11" s="1">
         <v>307</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>9</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>10</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1">
+        <v>309</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/NPCFunctionData.xlsx
+++ b/Datas/NPCFunctionData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
   <si>
     <t>id</t>
   </si>
@@ -108,6 +108,13 @@
   </si>
   <si>
     <t>F_AnimalLeave</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>closeTalk</t>
+  </si>
+  <si>
+    <t>bool</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -445,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:E13"/>
+  <dimension ref="A2:F13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -456,7 +463,7 @@
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -472,8 +479,11 @@
       <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F2" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -489,8 +499,11 @@
       <c r="E3" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F3" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -506,8 +519,11 @@
       <c r="E4" s="1">
         <v>300</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F4" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -523,8 +539,11 @@
       <c r="E5" s="1">
         <v>301</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F5" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -540,8 +559,11 @@
       <c r="E6" s="1">
         <v>302</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F6" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -557,8 +579,11 @@
       <c r="E7" s="1">
         <v>303</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F7" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -574,8 +599,11 @@
       <c r="E8" s="1">
         <v>304</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F8" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -591,8 +619,11 @@
       <c r="E9" s="1">
         <v>305</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F9" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -608,8 +639,11 @@
       <c r="E10" s="1">
         <v>306</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F10" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -625,8 +659,11 @@
       <c r="E11" s="1">
         <v>307</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F11" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -642,8 +679,11 @@
       <c r="E12" s="1">
         <v>308</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F12" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -658,6 +698,9 @@
       </c>
       <c r="E13" s="1">
         <v>309</v>
+      </c>
+      <c r="F13" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/NPCFunctionData.xlsx
+++ b/Datas/NPCFunctionData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
   <si>
     <t>id</t>
   </si>
@@ -115,6 +115,14 @@
   </si>
   <si>
     <t>bool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>投喂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F_Feeding</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -452,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:F13"/>
+  <dimension ref="A2:F14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -703,6 +711,26 @@
         <v>1</v>
       </c>
     </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>11</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1">
+        <v>310</v>
+      </c>
+      <c r="F14" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datas/NPCFunctionData.xlsx
+++ b/Datas/NPCFunctionData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
   <si>
     <t>id</t>
   </si>
@@ -122,7 +122,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>天气</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>F_Feeding</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F_Weather</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -460,7 +468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:F14"/>
+  <dimension ref="A2:F15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -719,7 +727,7 @@
         <v>28</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -728,6 +736,26 @@
         <v>310</v>
       </c>
       <c r="F14" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>12</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1">
+        <v>311</v>
+      </c>
+      <c r="F15" s="1" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Datas/NPCFunctionData.xlsx
+++ b/Datas/NPCFunctionData.xlsx
@@ -536,7 +536,7 @@
         <v>300</v>
       </c>
       <c r="F4" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">

--- a/Datas/NPCFunctionData.xlsx
+++ b/Datas/NPCFunctionData.xlsx
@@ -100,37 +100,39 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>放生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>投喂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>天气</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F_Feeding</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F_Weather</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>closeTalk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>F_SetAnimal</t>
-  </si>
-  <si>
-    <t>放生</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>F_AnimalLeave</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>closeTalk</t>
-  </si>
-  <si>
-    <t>bool</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>投喂</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>天气</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>F_Feeding</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>F_Weather</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -496,7 +498,7 @@
         <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -516,7 +518,7 @@
         <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -535,7 +537,7 @@
       <c r="E4" s="1">
         <v>300</v>
       </c>
-      <c r="F4" s="1" t="b">
+      <c r="F4" s="1">
         <v>1</v>
       </c>
     </row>
@@ -555,7 +557,7 @@
       <c r="E5" s="1">
         <v>301</v>
       </c>
-      <c r="F5" s="1" t="b">
+      <c r="F5" s="1">
         <v>0</v>
       </c>
     </row>
@@ -575,7 +577,7 @@
       <c r="E6" s="1">
         <v>302</v>
       </c>
-      <c r="F6" s="1" t="b">
+      <c r="F6" s="1">
         <v>0</v>
       </c>
     </row>
@@ -595,7 +597,7 @@
       <c r="E7" s="1">
         <v>303</v>
       </c>
-      <c r="F7" s="1" t="b">
+      <c r="F7" s="1">
         <v>0</v>
       </c>
     </row>
@@ -615,7 +617,7 @@
       <c r="E8" s="1">
         <v>304</v>
       </c>
-      <c r="F8" s="1" t="b">
+      <c r="F8" s="1">
         <v>0</v>
       </c>
     </row>
@@ -635,7 +637,7 @@
       <c r="E9" s="1">
         <v>305</v>
       </c>
-      <c r="F9" s="1" t="b">
+      <c r="F9" s="1">
         <v>0</v>
       </c>
     </row>
@@ -655,7 +657,7 @@
       <c r="E10" s="1">
         <v>306</v>
       </c>
-      <c r="F10" s="1" t="b">
+      <c r="F10" s="1">
         <v>0</v>
       </c>
     </row>
@@ -675,7 +677,7 @@
       <c r="E11" s="1">
         <v>307</v>
       </c>
-      <c r="F11" s="1" t="b">
+      <c r="F11" s="1">
         <v>0</v>
       </c>
     </row>
@@ -687,7 +689,7 @@
         <v>21</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
@@ -695,8 +697,8 @@
       <c r="E12" s="1">
         <v>308</v>
       </c>
-      <c r="F12" s="1" t="b">
-        <v>1</v>
+      <c r="F12" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -704,10 +706,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
@@ -715,8 +717,8 @@
       <c r="E13" s="1">
         <v>309</v>
       </c>
-      <c r="F13" s="1" t="b">
-        <v>1</v>
+      <c r="F13" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -724,10 +726,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -735,8 +737,8 @@
       <c r="E14" s="1">
         <v>310</v>
       </c>
-      <c r="F14" s="1" t="b">
-        <v>1</v>
+      <c r="F14" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
@@ -744,10 +746,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -755,13 +757,13 @@
       <c r="E15" s="1">
         <v>311</v>
       </c>
-      <c r="F15" s="1" t="b">
+      <c r="F15" s="1">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Datas/NPCFunctionData.xlsx
+++ b/Datas/NPCFunctionData.xlsx
@@ -572,7 +572,7 @@
         <v>20</v>
       </c>
       <c r="D6" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E6" s="1">
         <v>302</v>
@@ -592,7 +592,7 @@
         <v>19</v>
       </c>
       <c r="D7" s="1">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="E7" s="1">
         <v>303</v>
